--- a/Epreuve - E6/Projet_NetCorp_BTS_Adrien_D/RealisationReseau/plan_adressage_ip.xlsx
+++ b/Epreuve - E6/Projet_NetCorp_BTS_Adrien_D/RealisationReseau/plan_adressage_ip.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\Documents\GitHub\DEMANGE\Projet_NetCorp_BTS_Adrien_D\RealisationReseau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Adrien\Documents\GitHub\DEMANGE\Epreuve - E6\Projet_NetCorp_BTS_Adrien_D\RealisationReseau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0791E6FD-F6E9-450D-B294-8D3934C32F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2536EF-71AB-49FE-8AA4-8CC9432B613A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{36BEBFB1-396A-42C2-8A18-1D22A8D3F89B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>VLAN</t>
   </si>
@@ -59,24 +59,6 @@
     <t>IT</t>
   </si>
   <si>
-    <t>192.168.21.0/24</t>
-  </si>
-  <si>
-    <t>192.168.31.0/24</t>
-  </si>
-  <si>
-    <t>192.168.61.0/24</t>
-  </si>
-  <si>
-    <t>192.168.21.1</t>
-  </si>
-  <si>
-    <t>192.168.31.1</t>
-  </si>
-  <si>
-    <t>192.168.61.1</t>
-  </si>
-  <si>
     <t>Nom Machine</t>
   </si>
   <si>
@@ -101,28 +83,46 @@
     <t>LTP-LAB-02</t>
   </si>
   <si>
-    <t>192.168.61.10</t>
-  </si>
-  <si>
-    <t>192.168.61.20</t>
-  </si>
-  <si>
-    <t>192.168.61.30</t>
-  </si>
-  <si>
-    <t>192.168.21.100</t>
-  </si>
-  <si>
-    <t>192.168.31.100</t>
-  </si>
-  <si>
-    <t>61 - IT</t>
-  </si>
-  <si>
-    <t>21 - RH</t>
-  </si>
-  <si>
-    <t>31 - Direction</t>
+    <t>223 - IT</t>
+  </si>
+  <si>
+    <t>221 - RH</t>
+  </si>
+  <si>
+    <t>222 - Direction</t>
+  </si>
+  <si>
+    <t>192.168.223.10</t>
+  </si>
+  <si>
+    <t>192.168.223.20</t>
+  </si>
+  <si>
+    <t>192.168.223.30</t>
+  </si>
+  <si>
+    <t>192.168.221.1</t>
+  </si>
+  <si>
+    <t>192.168.222.1</t>
+  </si>
+  <si>
+    <t>192.168.223.1</t>
+  </si>
+  <si>
+    <t>192.168.221.0/24</t>
+  </si>
+  <si>
+    <t>192.168.222.0/24</t>
+  </si>
+  <si>
+    <t>192.168.223.0/24</t>
+  </si>
+  <si>
+    <t>DEBIAN-VPN</t>
+  </si>
+  <si>
+    <t>192.168.223.40</t>
   </si>
 </sst>
 </file>
@@ -158,9 +158,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -218,26 +221,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC202737-46BB-4565-AEB4-840122501FA8}" name="Table1" displayName="Table1" ref="D1:G4" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC202737-46BB-4565-AEB4-840122501FA8}" name="Table1" displayName="Table1" ref="D1:G4" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="D1:G4" xr:uid="{BC202737-46BB-4565-AEB4-840122501FA8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5EA8ECA5-A6D9-4685-93F8-3F8938FE5752}" name="VLAN" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{FC468D6C-DAA0-4195-BC7E-432FCDDA83EE}" name="Service" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{263A7C1A-99AF-4CC9-A822-1521CEFC3A47}" name="Réseau" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{83F63E7B-8E48-41C6-83C3-35244C5F82F0}" name="Passerelle" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5EA8ECA5-A6D9-4685-93F8-3F8938FE5752}" name="VLAN" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{FC468D6C-DAA0-4195-BC7E-432FCDDA83EE}" name="Service" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{263A7C1A-99AF-4CC9-A822-1521CEFC3A47}" name="Réseau" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{83F63E7B-8E48-41C6-83C3-35244C5F82F0}" name="Passerelle" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07145FD2-BF72-46CA-83B0-FDB3A44F578A}" name="Table2" displayName="Table2" ref="D6:G11" totalsRowShown="0" headerRowDxfId="6" dataDxfId="7">
-  <autoFilter ref="D6:G11" xr:uid="{07145FD2-BF72-46CA-83B0-FDB3A44F578A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{07145FD2-BF72-46CA-83B0-FDB3A44F578A}" name="Table2" displayName="Table2" ref="D6:G12" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="D6:G12" xr:uid="{07145FD2-BF72-46CA-83B0-FDB3A44F578A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{182C16A2-B887-4551-9CC8-877E05AC4814}" name="Nom Machine" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{8E109091-58F9-446C-A53F-06146690B24A}" name="VLAN Attribué " dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{8A073C66-D03B-4F7E-841E-0A138F9B718A}" name="Adresse IP " dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B56D7AAD-8EF6-488E-8CF7-E8E74C7A50D1}" name="Passerelle" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{182C16A2-B887-4551-9CC8-877E05AC4814}" name="Nom Machine" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{8E109091-58F9-446C-A53F-06146690B24A}" name="VLAN Attribué " dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{8A073C66-D03B-4F7E-841E-0A138F9B718A}" name="Adresse IP " dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{B56D7AAD-8EF6-488E-8CF7-E8E74C7A50D1}" name="Passerelle" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF965194-E26E-496F-AFDD-4C5652DA1CC2}">
-  <dimension ref="D1:H11"/>
+  <dimension ref="D1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="17.88671875" customWidth="1"/>
@@ -586,58 +589,58 @@
     </row>
     <row r="2" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D2" s="1">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D3" s="1">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D4" s="1">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1"/>
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>3</v>
@@ -645,72 +648,86 @@
     </row>
     <row r="7" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="F11" s="2">
+        <v>192168221100</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="2">
+        <v>192168222100</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
